--- a/artfynd/A 18503-2024 artfynd.xlsx
+++ b/artfynd/A 18503-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419335</v>
+        <v>123419334</v>
       </c>
       <c r="B2" t="n">
-        <v>79387</v>
+        <v>58313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605193</v>
+        <v>605165</v>
       </c>
       <c r="R2" t="n">
-        <v>6777731</v>
+        <v>6777737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2310</t>
+          <t>2024_2311</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419334</v>
+        <v>123419335</v>
       </c>
       <c r="B3" t="n">
-        <v>58313</v>
+        <v>79389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +817,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605165</v>
+        <v>605193</v>
       </c>
       <c r="R3" t="n">
-        <v>6777737</v>
+        <v>6777731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2311</t>
+          <t>2024_2310</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 18503-2024 artfynd.xlsx
+++ b/artfynd/A 18503-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419334</v>
+        <v>123419335</v>
       </c>
       <c r="B2" t="n">
-        <v>58313</v>
+        <v>79390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605165</v>
+        <v>605193</v>
       </c>
       <c r="R2" t="n">
-        <v>6777737</v>
+        <v>6777731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2311</t>
+          <t>2024_2310</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419335</v>
+        <v>123419334</v>
       </c>
       <c r="B3" t="n">
-        <v>79389</v>
+        <v>58313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +817,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605193</v>
+        <v>605165</v>
       </c>
       <c r="R3" t="n">
-        <v>6777731</v>
+        <v>6777737</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2310</t>
+          <t>2024_2311</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 18503-2024 artfynd.xlsx
+++ b/artfynd/A 18503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419334</v>
       </c>
       <c r="B2" t="n">
-        <v>58313</v>
+        <v>58319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419335</v>
       </c>
       <c r="B3" t="n">
-        <v>79393</v>
+        <v>79399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18503-2024 artfynd.xlsx
+++ b/artfynd/A 18503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419334</v>
       </c>
       <c r="B2" t="n">
-        <v>58319</v>
+        <v>58322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419335</v>
       </c>
       <c r="B3" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18503-2024 artfynd.xlsx
+++ b/artfynd/A 18503-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419334</v>
       </c>
       <c r="B2" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419335</v>
       </c>
       <c r="B3" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18503-2024 artfynd.xlsx
+++ b/artfynd/A 18503-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419334</v>
+        <v>123419335</v>
       </c>
       <c r="B2" t="n">
-        <v>58323</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605165</v>
+        <v>605193</v>
       </c>
       <c r="R2" t="n">
-        <v>6777737</v>
+        <v>6777731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2311</t>
+          <t>2024_2310</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419335</v>
+        <v>123419334</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>58323</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +817,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605193</v>
+        <v>605165</v>
       </c>
       <c r="R3" t="n">
-        <v>6777731</v>
+        <v>6777737</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2310</t>
+          <t>2024_2311</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 18503-2024 artfynd.xlsx
+++ b/artfynd/A 18503-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419335</v>
+        <v>123419334</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>58323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605193</v>
+        <v>605165</v>
       </c>
       <c r="R2" t="n">
-        <v>6777731</v>
+        <v>6777737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2310</t>
+          <t>2024_2311</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419334</v>
+        <v>123419335</v>
       </c>
       <c r="B3" t="n">
-        <v>58323</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +817,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605165</v>
+        <v>605193</v>
       </c>
       <c r="R3" t="n">
-        <v>6777737</v>
+        <v>6777731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2311</t>
+          <t>2024_2310</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
